--- a/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_EPIC_PLATFORM_CATALOG.xlsx
+++ b/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_EPIC_PLATFORM_CATALOG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epic Assets" sheetId="1" r:id="Rbd20df5242344d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epic Assets" sheetId="1" r:id="Rc67340ca4c914c7d"/>
   </x:sheets>
 </x:workbook>
 </file>
